--- a/output/pdf_financials_xlsx/SAGE.xlsx
+++ b/output/pdf_financials_xlsx/SAGE.xlsx
@@ -2204,13 +2204,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.346959</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.373389</v>
       </c>
     </row>
     <row r="93">
@@ -3746,7 +3746,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -4160,7 +4164,11 @@
           <t>Warrants reserve 7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SAGE.xlsx
+++ b/output/pdf_financials_xlsx/SAGE.xlsx
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.039628</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000495</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>-0.383702</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.117553</v>
+        <v>-4.157181</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.908492</v>
+        <v>-3.908987</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-4.884062</v>
@@ -987,10 +987,10 @@
         <v>-0.383702</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.117553</v>
+        <v>-4.157181</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.908492</v>
+        <v>-3.908987</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-4.884062</v>
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.621923</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.517363</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.108007</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009018</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.621923</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.517363</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.108007</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009018</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.6300559999999999</v>
+        <v>0.008133</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.022454</v>
+        <v>0.505091</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.326524</v>
+        <v>0.218517</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.817542</v>
+        <v>0.808524</v>
       </c>
     </row>
     <row r="49">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">

--- a/output/pdf_financials_xlsx/SAGE.xlsx
+++ b/output/pdf_financials_xlsx/SAGE.xlsx
@@ -2360,16 +2360,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003869</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.058563</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.039278</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.043148</v>
       </c>
     </row>
     <row r="102">
@@ -2455,16 +2455,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.070356</v>
+        <v>0.066487</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.799107</v>
+        <v>0.740544</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.609412</v>
+        <v>0.64869</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.302753</v>
+        <v>0.345901</v>
       </c>
     </row>
     <row r="107">
@@ -4488,7 +4488,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4524,7 +4528,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>-0.003869</v>
       </c>
@@ -4794,7 +4802,11 @@
           <t>Shares issued for cash, net 9</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5320,7 +5332,11 @@
           <t>Shares issued for cash, net 7</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5540,7 +5556,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>0.9855</v>
       </c>
